--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="514">
   <si>
     <t>Filename</t>
   </si>
@@ -811,16 +811,46 @@
     <t>0,0,1,1</t>
   </si>
   <si>
-    <t>0.9851,0.0070,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.0146,0.0000,0.0000,0.9978</t>
-  </si>
-  <si>
-    <t>0.9070,0.0716,0.0157,0.0035</t>
-  </si>
-  <si>
-    <t>0.5126,0.0012,0.0031,0.6958</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9926,0.0044,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.1391,0.0001,0.0003,0.9725</t>
+  </si>
+  <si>
+    <t>0.9751,0.0145,0.0038,0.0022</t>
+  </si>
+  <si>
+    <t>0.7114,0.0009,0.0028,0.4765</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0042,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9924,0.0083,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
@@ -829,724 +859,703 @@
     <t>0.9990,0.0009,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.0557,0.2920,0.6888,0.0005</t>
+  </si>
+  <si>
+    <t>0.0532,0.1091,0.8909,0.0009</t>
+  </si>
+  <si>
+    <t>0.2000,0.0549,0.7052,0.0016</t>
+  </si>
+  <si>
+    <t>0.0221,0.0207,0.9620,0.0130</t>
+  </si>
+  <si>
+    <t>0.7336,0.0173,0.2094,0.0154</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.1546,0.8452,0.0041,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6782,0.0048,0.0869,0.0592</t>
+  </si>
+  <si>
+    <t>0.6922,0.0162,0.2338,0.0131</t>
+  </si>
+  <si>
+    <t>0.0027,0.0054,0.9899,0.0048</t>
+  </si>
+  <si>
+    <t>0.0315,0.0239,0.9310,0.0103</t>
+  </si>
+  <si>
+    <t>0.0112,0.0043,0.9828,0.0060</t>
+  </si>
+  <si>
+    <t>0.0017,0.0029,0.9920,0.0349</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9976,0.0321</t>
+  </si>
+  <si>
+    <t>0.0580,0.9318,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.8810,0.0592,0.0327,0.0012</t>
+  </si>
+  <si>
+    <t>0.0001,0.0044,0.9996,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.0606,0.0000</t>
+  </si>
+  <si>
+    <t>0.9859,0.0083,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.1076,0.0502,0.8782,0.0022</t>
+  </si>
+  <si>
+    <t>0.4628,0.5545,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.9818,0.0576,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9966,0.0098,0.0034</t>
+  </si>
+  <si>
+    <t>0.0055,0.1252,0.1839,0.5804</t>
+  </si>
+  <si>
+    <t>0.0386,0.3049,0.5535,0.0385</t>
+  </si>
+  <si>
+    <t>0.0063,0.0023,0.7994,0.5540</t>
+  </si>
+  <si>
+    <t>0.0045,0.7586,0.6885,0.0075</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0106,0.9927,0.0089</t>
+  </si>
+  <si>
+    <t>0.0017,0.6470,0.1204,0.4846</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.8420,0.7670,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.9751,0.7468,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0070,0.9781,0.0104</t>
+  </si>
+  <si>
+    <t>0.0105,0.0020,0.9841,0.0089</t>
+  </si>
+  <si>
+    <t>0.0069,0.0061,0.9887,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0082,0.9980,0.0446</t>
+  </si>
+  <si>
+    <t>0.9932,0.0075,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0049,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0044,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1043,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0040,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0025,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9805,0.0233,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0097,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0746,0.9830,0.0027</t>
+  </si>
+  <si>
+    <t>0.0020,0.0674,0.9829,0.0064</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.1952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9987,0.0221</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6028,0.0919,0.2524,0.0006</t>
+  </si>
+  <si>
+    <t>0.9173,0.1039,0.0027,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0108,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.6828,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9958,0.6535,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7140,0.0000</t>
+  </si>
+  <si>
+    <t>0.1357,0.0015,0.0038,0.9341</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0037,0.0006,0.0011,0.9980</t>
+  </si>
+  <si>
+    <t>0.0048,0.0001,0.0000,0.9991</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0797,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9510,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9976,0.0647,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9855,0.5784,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.2703,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.0717,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0045,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9753,0.0346,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0081,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0057,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9741,0.0328,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0054,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0043,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.0986,0.9908,0.0024</t>
+  </si>
+  <si>
+    <t>0.9927,0.0008,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0047,0.0036,0.9897,0.0189</t>
+  </si>
+  <si>
+    <t>0.0009,0.9985,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.9900,0.0103,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.9943,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6631,0.3867,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.8479,0.1128,0.0202,0.0056</t>
+  </si>
+  <si>
+    <t>0.1203,0.0076,0.8419,0.0399</t>
+  </si>
+  <si>
+    <t>0.2873,0.5491,0.1282,0.0030</t>
+  </si>
+  <si>
+    <t>0.7244,0.0699,0.0870,0.0154</t>
+  </si>
+  <si>
+    <t>0.0007,0.3413,0.0030,0.9562</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.2456,0.6610,0.0227,0.0001</t>
+  </si>
+  <si>
+    <t>0.2792,0.6640,0.0139,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0003,0.0001</t>
+  </si>
+  <si>
     <t>0.9994,0.0005,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9993,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0079,0.0003,0.0000</t>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9950,0.0041,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9879,0.2812,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9592,0.8598,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.4644,0.9835,0.0018</t>
+  </si>
+  <si>
+    <t>0.0021,0.6193,0.9632,0.0044</t>
+  </si>
+  <si>
+    <t>0.9635,0.0063,0.0086,0.0009</t>
+  </si>
+  <si>
+    <t>0.9581,0.0182,0.0109,0.0026</t>
+  </si>
+  <si>
+    <t>0.1026,0.0053,0.9220,0.0006</t>
+  </si>
+  <si>
+    <t>0.8492,0.0592,0.0314,0.0032</t>
+  </si>
+  <si>
+    <t>0.4070,0.0038,0.0067,0.7825</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0526,0.0002,0.0003,0.9874</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0672,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0540,0.9401,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0013,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7704,0.2674,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9049,0.0014,0.0045,0.1412</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0168,0.3158,0.9563,0.0036</t>
+  </si>
+  <si>
+    <t>0.9891,0.0016,0.0018,0.0058</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.7531,0.3727,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9748,0.0183,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.8908,0.0992,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.0718,0.9077,0.0125,0.0001</t>
+  </si>
+  <si>
+    <t>0.7556,0.2510,0.0104,0.0003</t>
+  </si>
+  <si>
+    <t>0.9870,0.0089,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5143,0.5218,0.0040,0.0001</t>
+  </si>
+  <si>
+    <t>0.2301,0.7564,0.0067,0.0000</t>
+  </si>
+  <si>
+    <t>0.8294,0.1721,0.0048,0.0001</t>
+  </si>
+  <si>
+    <t>0.7881,0.1783,0.0092,0.0005</t>
+  </si>
+  <si>
+    <t>0.9627,0.0479,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0020,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9240,0.0889,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0610,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9635,0.0212,0.0104,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.3984,0.9081,0.0531</t>
+  </si>
+  <si>
+    <t>0.0018,0.0059,0.9953,0.0076</t>
+  </si>
+  <si>
+    <t>0.0262,0.2728,0.8395,0.0030</t>
+  </si>
+  <si>
+    <t>0.0002,0.0126,0.9991,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0031,0.9999,0.0019</t>
+  </si>
+  <si>
+    <t>0.0547,0.0956,0.8303,0.0060</t>
+  </si>
+  <si>
+    <t>0.0317,0.0295,0.9448,0.0027</t>
+  </si>
+  <si>
+    <t>0.6540,0.2010,0.0694,0.0015</t>
+  </si>
+  <si>
+    <t>0.0035,0.8143,0.8149,0.0004</t>
+  </si>
+  <si>
+    <t>0.0135,0.9434,0.0696,0.0024</t>
+  </si>
+  <si>
+    <t>0.2024,0.1480,0.5141,0.0031</t>
+  </si>
+  <si>
+    <t>0.9544,0.0098,0.0115,0.0015</t>
+  </si>
+  <si>
+    <t>0.8351,0.0871,0.0501,0.0006</t>
+  </si>
+  <si>
+    <t>0.0157,0.9722,0.0051,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9959,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.3110,0.6557,0.0074,0.0000</t>
+  </si>
+  <si>
+    <t>0.1823,0.8393,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0920,0.8975,0.0051,0.0000</t>
+  </si>
+  <si>
+    <t>0.0173,0.9575,0.0302,0.0016</t>
+  </si>
+  <si>
+    <t>0.9665,0.0042,0.0100,0.0033</t>
+  </si>
+  <si>
+    <t>0.9279,0.0313,0.0038,0.0085</t>
+  </si>
+  <si>
+    <t>0.6693,0.1383,0.0443,0.0084</t>
+  </si>
+  <si>
+    <t>0.9359,0.0083,0.0404,0.0037</t>
+  </si>
+  <si>
+    <t>0.0006,0.0018,0.9984,0.0045</t>
+  </si>
+  <si>
+    <t>0.0006,0.6523,0.0264,0.6943</t>
+  </si>
+  <si>
+    <t>0.0098,0.5390,0.7848,0.0088</t>
+  </si>
+  <si>
+    <t>0.0893,0.2171,0.4844,0.0104</t>
+  </si>
+  <si>
+    <t>0.0054,0.6343,0.4311,0.0315</t>
+  </si>
+  <si>
+    <t>0.9984,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8205,0.2176,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.9892,0.0114,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0074,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9906,0.0111,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9869,0.0162,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.1921,0.9917,0.0006</t>
+  </si>
+  <si>
+    <t>0.2470,0.7018,0.0256,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0033,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0018,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0958,0.9970,0.0058</t>
+  </si>
+  <si>
+    <t>0.0281,0.1842,0.7783,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9991,0.0053</t>
+  </si>
+  <si>
+    <t>0.2090,0.0160,0.7692,0.0039</t>
+  </si>
+  <si>
+    <t>0.0003,0.0011,0.9981,0.0108</t>
+  </si>
+  <si>
+    <t>0.0164,0.0356,0.9338,0.0283</t>
+  </si>
+  <si>
+    <t>0.0121,0.5912,0.8723,0.0022</t>
+  </si>
+  <si>
+    <t>0.9029,0.0009,0.0037,0.0367</t>
+  </si>
+  <si>
+    <t>0.3084,0.1869,0.2700,0.0107</t>
+  </si>
+  <si>
+    <t>0.3689,0.0319,0.5433,0.0600</t>
+  </si>
+  <si>
+    <t>0.9939,0.0065,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0027,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0044,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9719,0.0372,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.3483,0.4095,0.1886,0.0028</t>
-  </si>
-  <si>
-    <t>0.0061,0.3654,0.9232,0.0008</t>
-  </si>
-  <si>
-    <t>0.3756,0.0240,0.5899,0.0013</t>
-  </si>
-  <si>
-    <t>0.0040,0.0166,0.9902,0.0036</t>
-  </si>
-  <si>
-    <t>0.8782,0.0149,0.0959,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.2160,0.7933,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8367,0.0170,0.0672,0.0110</t>
-  </si>
-  <si>
-    <t>0.0828,0.1177,0.5331,0.0924</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.9986,0.0058</t>
-  </si>
-  <si>
-    <t>0.0553,0.0264,0.8940,0.0235</t>
-  </si>
-  <si>
-    <t>0.0115,0.0024,0.9850,0.0014</t>
-  </si>
-  <si>
-    <t>0.0021,0.0013,0.9951,0.0051</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9978,0.1557</t>
-  </si>
-  <si>
-    <t>0.0312,0.9639,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.8289,0.1274,0.0195,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0023,0.9999,0.0006</t>
-  </si>
-  <si>
-    <t>0.0004,0.9852,0.4200,0.0000</t>
-  </si>
-  <si>
-    <t>0.9599,0.0291,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.0639,0.0898,0.9175,0.0014</t>
-  </si>
-  <si>
-    <t>0.1875,0.7821,0.0138,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.9855,0.0243,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9974,0.0140,0.0037</t>
-  </si>
-  <si>
-    <t>0.0026,0.2142,0.1532,0.6539</t>
-  </si>
-  <si>
-    <t>0.2079,0.0125,0.0968,0.3572</t>
-  </si>
-  <si>
-    <t>0.0033,0.0030,0.9930,0.0032</t>
-  </si>
-  <si>
-    <t>0.0061,0.1327,0.9507,0.0064</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.0105,0.9836,0.0231</t>
-  </si>
-  <si>
-    <t>0.0002,0.9671,0.0284,0.2740</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0384,0.4090,0.4303,0.0037</t>
-  </si>
-  <si>
-    <t>0.0003,0.8362,0.9591,0.0002</t>
-  </si>
-  <si>
-    <t>0.0098,0.0646,0.9453,0.0241</t>
-  </si>
-  <si>
-    <t>0.0024,0.0010,0.9937,0.0113</t>
-  </si>
-  <si>
-    <t>0.0003,0.0073,0.9988,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.0124,0.9962,0.0388</t>
-  </si>
-  <si>
-    <t>0.9715,0.0394,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0018,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0072,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0479,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9585,0.0471,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0446,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0853,0.9790,0.0019</t>
-  </si>
-  <si>
-    <t>0.0027,0.2423,0.9599,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0741,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0179,0.9992,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6393,0.1515,0.1028,0.0003</t>
-  </si>
-  <si>
-    <t>0.4044,0.5607,0.0324,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0297,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.8172,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.0447,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0096,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.7299,0.0000</t>
-  </si>
-  <si>
-    <t>0.0258,0.0003,0.0005,0.9921</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0054,0.0000,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.0045,0.0019,0.0007,0.9978</t>
-  </si>
-  <si>
-    <t>0.0150,0.0002,0.0001,0.9965</t>
-  </si>
-  <si>
-    <t>0.0047,0.0008,0.0010,0.9978</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.4747,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9916,0.9566,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9983,0.2605,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9890,0.7150,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0839,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0277,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0022,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9593,0.0551,0.0007,0.0000</t>
+    <t>0.9990,0.0010,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9980,0.0019,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9979,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0041,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0031,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0145,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0027,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0026,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0052,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0076,0.9992,0.0016</t>
-  </si>
-  <si>
-    <t>0.9871,0.0011,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0021,0.9936,0.2143</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0142,0.9797,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0049,0.9902,0.0054,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.5818,0.4554,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.6648,0.2646,0.0350,0.0024</t>
-  </si>
-  <si>
-    <t>0.9440,0.0062,0.0164,0.0045</t>
-  </si>
-  <si>
-    <t>0.3082,0.4153,0.1823,0.0046</t>
-  </si>
-  <si>
-    <t>0.4965,0.2248,0.0851,0.0162</t>
-  </si>
-  <si>
-    <t>0.0032,0.4614,0.0227,0.6466</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.9950,0.0072,0.0000</t>
-  </si>
-  <si>
-    <t>0.2813,0.6350,0.0190,0.0001</t>
-  </si>
-  <si>
-    <t>0.5275,0.4182,0.0130,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0019,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0020,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0090,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9928,0.0097,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9910,0.0085,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.0342,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.9314,0.9382,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.0585,0.9720,0.0006</t>
-  </si>
-  <si>
-    <t>0.0128,0.4705,0.8741,0.0033</t>
-  </si>
-  <si>
-    <t>0.9048,0.0323,0.0189,0.0037</t>
-  </si>
-  <si>
-    <t>0.8896,0.0521,0.0443,0.0075</t>
-  </si>
-  <si>
-    <t>0.0175,0.0037,0.9798,0.0031</t>
-  </si>
-  <si>
-    <t>0.6671,0.2808,0.0191,0.0017</t>
-  </si>
-  <si>
-    <t>0.1158,0.0017,0.0008,0.9559</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0100,0.0000,0.0000,0.9986</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.1106,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0677,0.9278,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2355,0.7460,0.0066,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9748,0.0015,0.0033,0.0220</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1831,0.1269,0.6713,0.0607</t>
-  </si>
-  <si>
-    <t>0.9298,0.0040,0.0205,0.0137</t>
-  </si>
-  <si>
-    <t>0.9959,0.0018,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.3415,0.6538,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.9045,0.0737,0.0188,0.0006</t>
-  </si>
-  <si>
-    <t>0.8592,0.1557,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.2069,0.7773,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.5841,0.4156,0.0112,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0125,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6418,0.3931,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.6523,0.3285,0.0080,0.0000</t>
-  </si>
-  <si>
-    <t>0.9598,0.0487,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9642,0.0303,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0140,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0047,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7324,0.3572,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0812,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0027,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0043,0.1996,0.7751,0.1822</t>
-  </si>
-  <si>
-    <t>0.0016,0.0088,0.9959,0.0034</t>
-  </si>
-  <si>
-    <t>0.0837,0.2533,0.5889,0.0038</t>
-  </si>
-  <si>
-    <t>0.0022,0.0041,0.9945,0.0032</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9992,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.0072,0.9989,0.0043</t>
-  </si>
-  <si>
-    <t>0.1033,0.0744,0.7546,0.0018</t>
-  </si>
-  <si>
-    <t>0.1117,0.0252,0.8224,0.0029</t>
-  </si>
-  <si>
-    <t>0.1720,0.4665,0.3588,0.0029</t>
-  </si>
-  <si>
-    <t>0.0240,0.6620,0.5854,0.0006</t>
-  </si>
-  <si>
-    <t>0.0125,0.9649,0.0281,0.0020</t>
-  </si>
-  <si>
-    <t>0.0952,0.2218,0.6131,0.0029</t>
-  </si>
-  <si>
-    <t>0.6366,0.1692,0.0275,0.0162</t>
-  </si>
-  <si>
-    <t>0.7796,0.1591,0.0348,0.0081</t>
-  </si>
-  <si>
-    <t>0.0118,0.9721,0.0123,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.9898,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.9943,0.0070,0.0000</t>
-  </si>
-  <si>
-    <t>0.3339,0.7174,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0427,0.9433,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.3700,0.6039,0.0148,0.0009</t>
-  </si>
-  <si>
-    <t>0.9538,0.0067,0.0215,0.0011</t>
-  </si>
-  <si>
-    <t>0.9690,0.0087,0.0029,0.0046</t>
-  </si>
-  <si>
-    <t>0.4210,0.2408,0.1507,0.0034</t>
-  </si>
-  <si>
-    <t>0.8590,0.0110,0.1146,0.0051</t>
-  </si>
-  <si>
-    <t>0.0014,0.0024,0.9969,0.0066</t>
-  </si>
-  <si>
-    <t>0.0017,0.5124,0.3134,0.2036</t>
-  </si>
-  <si>
-    <t>0.0008,0.9891,0.0101,0.0331</t>
-  </si>
-  <si>
-    <t>0.3061,0.0968,0.4034,0.0118</t>
-  </si>
-  <si>
-    <t>0.0059,0.4066,0.7706,0.0074</t>
-  </si>
-  <si>
-    <t>0.9802,0.0230,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0033,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9890,0.0115,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0044,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0097,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9868,0.0195,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.3811,0.9933,0.0021</t>
-  </si>
-  <si>
-    <t>0.1861,0.7855,0.0149,0.0002</t>
-  </si>
-  <si>
-    <t>0.8980,0.0420,0.0495,0.0020</t>
-  </si>
-  <si>
-    <t>0.0012,0.0044,0.9971,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0508,0.9990,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.6838,0.9890,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9995,0.0043</t>
-  </si>
-  <si>
-    <t>0.0588,0.0141,0.9096,0.0093</t>
-  </si>
-  <si>
-    <t>0.0006,0.0011,0.9990,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.0235,0.9802,0.0083</t>
-  </si>
-  <si>
-    <t>0.0021,0.8026,0.9136,0.0006</t>
-  </si>
-  <si>
-    <t>0.8793,0.0070,0.0479,0.0101</t>
-  </si>
-  <si>
-    <t>0.7944,0.0281,0.1237,0.0029</t>
-  </si>
-  <si>
-    <t>0.3677,0.0309,0.6307,0.0098</t>
-  </si>
-  <si>
-    <t>0.9865,0.0163,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0030,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0065,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9945,0.0065,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0014,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0268,0.3389,0.5777,0.0083</t>
-  </si>
-  <si>
-    <t>0.0007,0.1878,0.9836,0.0010</t>
-  </si>
-  <si>
-    <t>0.0100,0.3602,0.6097,0.0222</t>
-  </si>
-  <si>
-    <t>0.0094,0.2838,0.9056,0.0048</t>
-  </si>
-  <si>
-    <t>0.0001,0.0017,0.9993,0.0020</t>
-  </si>
-  <si>
-    <t>0.0635,0.0070,0.1805,0.7840</t>
-  </si>
-  <si>
-    <t>0.0052,0.0198,0.9866,0.0081</t>
-  </si>
-  <si>
-    <t>0.0038,0.0075,0.6243,0.7070</t>
-  </si>
-  <si>
-    <t>0.9638,0.0026,0.0149,0.0061</t>
-  </si>
-  <si>
-    <t>0.0003,0.0036,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.5659,0.0019,0.0104,0.5705</t>
+    <t>0.0076,0.9312,0.0782,0.0158</t>
+  </si>
+  <si>
+    <t>0.0001,0.4542,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.0074,0.7320,0.3331,0.0070</t>
+  </si>
+  <si>
+    <t>0.0426,0.1590,0.7828,0.0110</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9996,0.0009</t>
+  </si>
+  <si>
+    <t>0.1562,0.0100,0.5636,0.2089</t>
+  </si>
+  <si>
+    <t>0.0202,0.0828,0.9440,0.0133</t>
+  </si>
+  <si>
+    <t>0.0241,0.0364,0.1311,0.7744</t>
+  </si>
+  <si>
+    <t>0.9559,0.0003,0.0010,0.0449</t>
+  </si>
+  <si>
+    <t>0.0013,0.0064,0.0004,0.9987</t>
+  </si>
+  <si>
+    <t>0.5645,0.0009,0.0032,0.6383</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0008,0.0005,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.6469,0.0672,0.0514,0.2221</t>
+    <t>0.0005,0.0003,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.8485,0.0708,0.0354,0.0337</t>
   </si>
 </sst>
 </file>
@@ -1932,7 +1941,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1946,7 +1955,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1960,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1971,10 +1980,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1988,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2002,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2016,7 +2025,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2030,7 +2039,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2044,7 +2053,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2058,7 +2067,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2072,7 +2081,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2086,7 +2095,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2097,10 +2106,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2114,7 +2123,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2128,7 +2137,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2142,7 +2151,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2156,7 +2165,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2170,7 +2179,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2184,7 +2193,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2198,7 +2207,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2212,7 +2221,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2226,7 +2235,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2240,7 +2249,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2251,10 +2260,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2268,7 +2277,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2282,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2296,7 +2305,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2310,7 +2319,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2324,7 +2333,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2338,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2352,7 +2361,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2366,7 +2375,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2380,7 +2389,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2394,7 +2403,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2408,7 +2417,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2422,7 +2431,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2436,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2450,7 +2459,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2464,7 +2473,7 @@
         <v>260</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2475,10 +2484,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2489,10 +2498,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2503,10 +2512,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2520,7 +2529,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2534,7 +2543,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2548,7 +2557,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2562,7 +2571,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2576,7 +2585,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2590,7 +2599,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2601,10 +2610,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2618,7 +2627,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2632,7 +2641,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2646,7 +2655,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2660,7 +2669,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2674,7 +2683,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2688,7 +2697,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2702,7 +2711,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2716,7 +2725,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2730,7 +2739,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2744,7 +2753,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2758,7 +2767,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2772,7 +2781,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2786,7 +2795,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2800,7 +2809,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2814,7 +2823,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2828,7 +2837,7 @@
         <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2842,7 +2851,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2856,7 +2865,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2870,7 +2879,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2884,7 +2893,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2895,10 +2904,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2912,7 +2921,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2926,7 +2935,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2937,10 +2946,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2954,7 +2963,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2968,7 +2977,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2982,7 +2991,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2996,7 +3005,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3010,7 +3019,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3024,7 +3033,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3038,7 +3047,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3052,7 +3061,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3066,7 +3075,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3080,7 +3089,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3094,7 +3103,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3108,7 +3117,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3122,7 +3131,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3136,7 +3145,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3150,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3164,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3178,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3192,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3206,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3220,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3234,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3248,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3262,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3276,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3290,7 +3299,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3304,7 +3313,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3318,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3332,7 +3341,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3346,7 +3355,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3360,7 +3369,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3374,7 +3383,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3388,7 +3397,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3402,7 +3411,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3416,7 +3425,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3430,7 +3439,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3444,7 +3453,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3458,7 +3467,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3472,7 +3481,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3486,7 +3495,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3500,7 +3509,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3514,7 +3523,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3528,7 +3537,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3539,10 +3548,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3553,10 +3562,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3570,7 +3579,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3584,7 +3593,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3598,7 +3607,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>335</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3612,7 +3621,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3626,7 +3635,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3640,7 +3649,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3654,7 +3663,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3668,7 +3677,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3679,10 +3688,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3696,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3710,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3724,7 +3733,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3738,7 +3747,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3752,7 +3761,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3766,7 +3775,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3780,7 +3789,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3794,7 +3803,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3808,7 +3817,7 @@
         <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3822,7 +3831,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3836,7 +3845,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3847,10 +3856,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3864,7 +3873,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3878,7 +3887,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3892,7 +3901,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3906,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3920,7 +3929,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3934,7 +3943,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3948,7 +3957,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3962,7 +3971,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3976,7 +3985,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3990,7 +3999,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4004,7 +4013,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4018,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4029,10 +4038,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4046,7 +4055,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4060,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4074,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4088,7 +4097,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4102,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4116,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4127,10 +4136,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4144,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4158,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4172,7 +4181,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4186,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4200,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4214,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4228,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4242,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>321</v>
+        <v>276</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4256,7 +4265,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4270,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4284,7 +4293,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4298,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>426</v>
+        <v>367</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4312,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4323,10 +4332,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4337,10 +4346,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4354,7 +4363,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4368,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4382,7 +4391,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4396,7 +4405,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4410,7 +4419,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4424,7 +4433,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4438,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4452,7 +4461,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4466,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4480,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4494,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4508,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4522,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4536,7 +4545,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4550,7 +4559,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4564,7 +4573,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4578,7 +4587,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4592,7 +4601,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4606,7 +4615,7 @@
         <v>263</v>
       </c>
       <c r="D193" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4620,7 +4629,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4634,7 +4643,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4648,7 +4657,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4662,7 +4671,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4676,7 +4685,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4690,7 +4699,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4704,7 +4713,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4718,7 +4727,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4732,7 +4741,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4746,7 +4755,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4760,7 +4769,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4774,7 +4783,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4788,7 +4797,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4802,7 +4811,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4816,7 +4825,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4827,10 +4836,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4841,10 +4850,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4855,10 +4864,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4869,10 +4878,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4886,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4900,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4914,7 +4923,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4928,7 +4937,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4942,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4956,7 +4965,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4970,7 +4979,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4984,7 +4993,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>362</v>
+        <v>478</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4998,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5012,7 +5021,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5026,7 +5035,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5040,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5054,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5065,10 +5074,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5082,7 +5091,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5096,7 +5105,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5110,7 +5119,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5124,7 +5133,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5138,7 +5147,7 @@
         <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5152,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5163,10 +5172,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D233" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5180,7 +5189,7 @@
         <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5194,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5208,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5222,7 +5231,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5236,7 +5245,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5250,7 +5259,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5264,7 +5273,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5278,7 +5287,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5292,7 +5301,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5303,10 +5312,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5320,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5331,10 +5340,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D245" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5348,7 +5357,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5362,7 +5371,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5373,10 +5382,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5390,7 +5399,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5401,10 +5410,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D250" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5418,7 +5427,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5432,7 +5441,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5443,10 +5452,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D253" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5460,7 +5469,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5474,7 +5483,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5488,7 +5497,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
